--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487709_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487709_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.194699999999999</v>
+        <v>9.858700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9534</v>
+        <v>7.4539</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2413</v>
+        <v>2.4048</v>
       </c>
       <c r="G2" t="n">
         <v>4.9228</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1281</v>
+        <v>-0.464</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6046</v>
+        <v>-0.1041</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5235</v>
+        <v>-0.36</v>
       </c>
       <c r="V2" t="n">
         <v>4.2358</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7271</v>
+        <v>2.4362</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1928</v>
+        <v>-0.2929</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9199</v>
+        <v>2.7291</v>
       </c>
       <c r="G3" t="n">
         <v>2.9964</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6725</v>
+        <v>0.3816</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1233</v>
+        <v>0.0232</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5492</v>
+        <v>0.3584</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9133</v>
+        <v>1.7225</v>
       </c>
       <c r="E4" t="n">
         <v>-1.1305</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0438</v>
+        <v>2.853</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7726</v>
@@ -766,13 +766,13 @@
         <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4785</v>
+        <v>0.2877</v>
       </c>
       <c r="T4" t="n">
         <v>0.1233</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3551</v>
+        <v>0.1644</v>
       </c>
       <c r="V4" t="n">
         <v>3.9537</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6081</v>
+        <v>1.3718</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.481</v>
       </c>
       <c r="F5" t="n">
-        <v>1.027</v>
+        <v>0.8907</v>
       </c>
       <c r="G5" t="n">
         <v>1.869</v>
@@ -844,13 +844,13 @@
         <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1391</v>
+        <v>-0.0973</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1806</v>
+        <v>-0.2807</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3197</v>
+        <v>0.1834</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1761</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8544</v>
+        <v>0.8722</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6893</v>
+        <v>-1.8895</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5436</v>
+        <v>2.7617</v>
       </c>
       <c r="G6" t="n">
         <v>0.8641</v>
@@ -922,13 +922,13 @@
         <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3515</v>
+        <v>-0.3337</v>
       </c>
       <c r="T6" t="n">
-        <v>0.305</v>
+        <v>0.1048</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6565</v>
+        <v>-0.4385</v>
       </c>
       <c r="V6" t="n">
         <v>1.506</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0231</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9248</v>
+        <v>-0.3242</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9479</v>
+        <v>0.8389</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1167</v>
@@ -1000,13 +1000,13 @@
         <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6065</v>
+        <v>-0.115</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6662</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0597</v>
+        <v>-0.0493</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4121</v>
+        <v>-0.2392</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4686</v>
+        <v>-2.2684</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0565</v>
+        <v>2.0292</v>
       </c>
       <c r="G8" t="n">
         <v>0.528</v>
@@ -1078,13 +1078,13 @@
         <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.164</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4845</v>
+        <v>-0.2843</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3206</v>
+        <v>0.2933</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>O. PEÑA LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4627</v>
+        <v>-0.503</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4071</v>
+        <v>-0.7111</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8698</v>
+        <v>0.2081</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7812</v>
+        <v>-0.7217</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7234</v>
+        <v>0.276</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0578</v>
+        <v>-0.9977</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4626</v>
+        <v>0.4643</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5437</v>
+        <v>1.0504</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.5861</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3187</v>
+        <v>-1.186</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1796</v>
+        <v>-0.7744</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.139</v>
+        <v>-0.4115</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7961</v>
+        <v>-0.5574</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0637</v>
+        <v>-0.2053</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2676</v>
+        <v>-0.3522</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. PEÑA LOPEZ</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0124</v>
+        <v>-1.8096</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1115</v>
+        <v>0.0057</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09909999999999999</v>
+        <v>-1.8153</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7217</v>
+        <v>-0.7812</v>
       </c>
       <c r="H10" t="n">
-        <v>0.276</v>
+        <v>-0.7234</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9977</v>
+        <v>-0.0578</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4643</v>
+        <v>-0.4626</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0504</v>
+        <v>-0.5437</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5861</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.186</v>
+        <v>-0.3187</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7744</v>
+        <v>-0.1796</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4115</v>
+        <v>-0.139</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0668</v>
+        <v>0.4492</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6057</v>
+        <v>0.6623</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4612</v>
+        <v>-0.2131</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1118</v>
+        <v>-3.9027</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.999</v>
+        <v>-1.8989</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1128</v>
+        <v>-2.0038</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4514</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4067</v>
+        <v>-1.1976</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5451</v>
+        <v>-0.445</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8616</v>
+        <v>-0.7526</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4477</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.3217</v>
+        <v>10.3215</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5749000000000004</v>
+        <v>-0.5749000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>10.8965</v>
+        <v>10.8964</v>
       </c>
       <c r="G12" t="n">
         <v>7.336699999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7827000000000001</v>
+        <v>-0.7827000000000002</v>
       </c>
       <c r="I12" t="n">
         <v>8.119299999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>3.935500000000001</v>
+        <v>3.9355</v>
       </c>
       <c r="K12" t="n">
         <v>1.0711</v>
@@ -1372,7 +1372,7 @@
         <v>2.8644</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4012</v>
+        <v>3.401200000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-1.8538</v>
@@ -1390,13 +1390,13 @@
         <v>17.463</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6374</v>
+        <v>-1.6375</v>
       </c>
       <c r="T12" t="n">
         <v>-0.4714</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1661</v>
+        <v>-1.1662</v>
       </c>
       <c r="V12" t="n">
         <v>2.6822</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.5504</v>
+        <v>8.4756</v>
       </c>
       <c r="E13" t="n">
-        <v>10.2543</v>
+        <v>8.152200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2961</v>
+        <v>0.3233</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0624</v>
@@ -1468,13 +1468,13 @@
         <v>0.7761</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6576</v>
+        <v>1.5828</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3983</v>
+        <v>1.2962</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2593</v>
+        <v>0.2866</v>
       </c>
       <c r="V13" t="n">
         <v>7.3432</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1129</v>
+        <v>0.1615</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6483</v>
+        <v>0.2672</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7612</v>
+        <v>-0.1057</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.9767</v>
+        <v>2.0123</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2488</v>
+        <v>1.6642</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7279</v>
+        <v>0.3481</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.3023</v>
+        <v>2.6091</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6755</v>
+        <v>1.9773</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6267</v>
+        <v>0.6318</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6744</v>
+        <v>-0.5967</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4267</v>
+        <v>-0.3131</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1011</v>
+        <v>-0.2836</v>
       </c>
       <c r="P14" t="n">
-        <v>0.194</v>
+        <v>-0.194</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3284</v>
+        <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0015</v>
+        <v>-0.715</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8943</v>
+        <v>-0.4896</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1073</v>
+        <v>-0.2254</v>
       </c>
       <c r="V14" t="n">
-        <v>0.894</v>
+        <v>-0.9418</v>
       </c>
       <c r="W14" t="n">
-        <v>0.894</v>
+        <v>0.2821</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1982</v>
+        <v>0.1575</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4674</v>
+        <v>-1.5492</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2692</v>
+        <v>1.7067</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0123</v>
+        <v>-1.9767</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6642</v>
+        <v>-0.2488</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3481</v>
+        <v>-1.7279</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6091</v>
+        <v>-1.3023</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9773</v>
+        <v>-0.6755</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6318</v>
+        <v>-0.6267</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5967</v>
+        <v>-0.6744</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3131</v>
+        <v>0.4267</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2836</v>
+        <v>-1.1011</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.194</v>
+        <v>0.194</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9403</v>
+        <v>2.3284</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6783</v>
+        <v>1.0461</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2894</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3889</v>
+        <v>0.0527</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9418</v>
+        <v>0.894</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2059</v>
+        <v>0.0761</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2342</v>
+        <v>-0.034</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0283</v>
+        <v>0.1101</v>
       </c>
       <c r="G16" t="n">
         <v>2.5257</v>
@@ -1702,13 +1702,13 @@
         <v>0.5821</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4794</v>
+        <v>-0.1974</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3028</v>
+        <v>-0.1026</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1765</v>
+        <v>-0.0948</v>
       </c>
       <c r="V16" t="n">
         <v>-0.894</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>M. DEL VALLE REGALADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7682</v>
+        <v>-0.7668</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4283</v>
+        <v>-3.2369</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3399</v>
+        <v>2.4701</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0799</v>
+        <v>-0.139</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0974</v>
+        <v>0.3304</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1773</v>
+        <v>-0.4694</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.223</v>
+        <v>-0.1371</v>
       </c>
       <c r="K17" t="n">
-        <v>1.071</v>
+        <v>0.449</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2941</v>
+        <v>-0.5861</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1431</v>
+        <v>-0.0019</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0263</v>
+        <v>-0.1187</v>
       </c>
       <c r="O17" t="n">
         <v>0.1168</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5821</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.3881</v>
+        <v>-3.1045</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9702</v>
+        <v>2.5224</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2355</v>
+        <v>-0.0457</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1828</v>
+        <v>0.0047</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0527</v>
+        <v>-0.0504</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DEL VALLE REGALADO</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4497</v>
+        <v>-0.8044</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.1378</v>
+        <v>-0.3282</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6881</v>
+        <v>-0.4762</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.139</v>
+        <v>-0.0799</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3304</v>
+        <v>1.0974</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4694</v>
+        <v>-1.1773</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1371</v>
+        <v>-0.223</v>
       </c>
       <c r="K18" t="n">
-        <v>0.449</v>
+        <v>1.071</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5861</v>
+        <v>-1.2941</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0019</v>
+        <v>0.1431</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1187</v>
+        <v>0.0263</v>
       </c>
       <c r="O18" t="n">
         <v>0.1168</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5821</v>
+        <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1045</v>
+        <v>-0.3881</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5224</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7286</v>
+        <v>0.1994</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8962</v>
+        <v>0.2829</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1676</v>
+        <v>-0.0835</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4683</v>
+        <v>-2.1408</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4015</v>
+        <v>-0.1012</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0668</v>
+        <v>-2.0396</v>
       </c>
       <c r="G19" t="n">
         <v>0.613</v>
@@ -1936,13 +1936,13 @@
         <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7097</v>
+        <v>-0.3822</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6662</v>
+        <v>-0.3659</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0435</v>
+        <v>-0.0162</v>
       </c>
       <c r="V19" t="n">
         <v>-3.3418</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4647</v>
+        <v>-3.2913</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2655</v>
+        <v>-2.765</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1992</v>
+        <v>-0.5263</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2261</v>
@@ -2014,13 +2014,13 @@
         <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5211</v>
+        <v>0.6945</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4105</v>
+        <v>0.09</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9316</v>
+        <v>0.6046</v>
       </c>
       <c r="V20" t="n">
         <v>-2.7298</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6489</v>
+        <v>-3.3853</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8931</v>
+        <v>-2.793</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7558</v>
+        <v>-0.5923</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5579</v>
@@ -2092,13 +2092,13 @@
         <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.703</v>
+        <v>-0.4394</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5451</v>
+        <v>-0.445</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1579</v>
+        <v>0.0056</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8801</v>
+        <v>-3.4613</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2357</v>
+        <v>-3.7352</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3556</v>
+        <v>0.2738</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0148</v>
@@ -2170,13 +2170,13 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0309</v>
+        <v>0.3878</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1817</v>
+        <v>0.3188</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1508</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2821</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2972</v>
+        <v>-5.3423</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3738</v>
+        <v>-4.7732</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9233</v>
+        <v>-0.569</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4309</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4484</v>
+        <v>-0.4935</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0173</v>
+        <v>-0.4167</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4311</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2287,7 +2287,7 @@
         <v>-10.8965</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5751000000000002</v>
+        <v>0.5749000000000002</v>
       </c>
       <c r="G24" t="n">
         <v>-7.3367</v>
@@ -2332,10 +2332,10 @@
         <v>1.1662</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4713999999999999</v>
+        <v>0.4714</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.682200000000001</v>
+        <v>-2.6822</v>
       </c>
       <c r="W24" t="n">
         <v>8.801399999999999</v>
